--- a/banks/W15_Kahoot匯入.xlsx
+++ b/banks/W15_Kahoot匯入.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -491,30 +491,30 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
+          <t>質子動力</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>電子傳遞鏈</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
           <t>氧化磷酸化</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>鐵硫中心</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>質子動力</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>電子傳遞鏈</t>
-        </is>
-      </c>
       <c r="F2" s="2" t="n">
         <v>30</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -531,25 +531,25 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
+          <t>鐵硫中心</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
           <t>ATP合成酶</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>電子傳遞鏈</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>鐵硫中心</t>
-        </is>
-      </c>
       <c r="F3" s="2" t="n">
         <v>30</v>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -561,19 +561,19 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
+          <t>複合體</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>呼吸鏈</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>基質</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>複合體</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>呼吸鏈</t>
-        </is>
-      </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
           <t>解偶聯劑</t>
@@ -584,7 +584,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -596,19 +596,19 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
+          <t>膜間隙</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
           <t>呼吸鏈</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>複合體</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>膜間隙</t>
-        </is>
-      </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
           <t>鐵硫中心</t>
@@ -619,7 +619,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -631,30 +631,30 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
+          <t>泛醌</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
           <t>基質</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>呼吸鏈</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>質子動力</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>泛醌</t>
-        </is>
-      </c>
       <c r="F6" s="2" t="n">
         <v>30</v>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -666,19 +666,19 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
+          <t>氧化磷酸化</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
           <t>化學滲透</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>細胞色素c</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>氧化磷酸化</t>
-        </is>
-      </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
           <t>電子傳遞鏈</t>
@@ -689,7 +689,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -701,30 +701,30 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
+          <t>質子動力</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>化學滲透</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>解偶聯劑</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>鐵硫中心</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>質子動力</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>解偶聯劑</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>化學滲透</t>
-        </is>
-      </c>
       <c r="F8" s="2" t="n">
         <v>30</v>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -741,25 +741,25 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>氰化物</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
           <t>內膜</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>呼吸鏈</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>氰化物</t>
-        </is>
-      </c>
       <c r="F9" s="2" t="n">
         <v>30</v>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -771,30 +771,30 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
+          <t>氰化物</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>複合體</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>內膜</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>膜間隙</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>複合體</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>氰化物</t>
-        </is>
-      </c>
       <c r="F10" s="2" t="n">
         <v>30</v>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -806,30 +806,30 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
+          <t>膜間隙</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
           <t>基質</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>質子動力</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>泛醌</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>膜間隙</t>
-        </is>
-      </c>
       <c r="F11" s="2" t="n">
         <v>30</v>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -846,25 +846,25 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>質子梯度</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
           <t>鐵硫中心</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>複合體</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>質子梯度</t>
-        </is>
-      </c>
       <c r="F12" s="2" t="n">
         <v>30</v>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -876,30 +876,30 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
+          <t>解偶聯劑</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>化學滲透</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>細胞色素c</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>化學滲透</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>質子動力</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>解偶聯劑</t>
-        </is>
-      </c>
       <c r="F13" s="2" t="n">
         <v>30</v>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -911,30 +911,30 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
+          <t>化學滲透</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>氰化物</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
           <t>膜間隙</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>鐵硫中心</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>氰化物</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>化學滲透</t>
-        </is>
-      </c>
       <c r="F14" s="2" t="n">
         <v>30</v>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -946,30 +946,30 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
+          <t>ATP合成酶</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>化學滲透</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
           <t>解偶聯劑</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>化學滲透</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>氧化磷酸化</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>ATP合成酶</t>
-        </is>
-      </c>
       <c r="F15" s="2" t="n">
         <v>30</v>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -981,30 +981,30 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
+          <t>氧化磷酸化</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>細胞色素c</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>解偶聯劑</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>質子動力</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>細胞色素c</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>氧化磷酸化</t>
-        </is>
-      </c>
       <c r="F16" s="2" t="n">
         <v>30</v>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -1016,30 +1016,30 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
+          <t>膜間隙</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>呼吸鏈</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>質子動力</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
           <t>氰化物</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>呼吸鏈</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>膜間隙</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>質子動力</t>
-        </is>
-      </c>
       <c r="F17" s="2" t="n">
         <v>30</v>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -1051,30 +1051,170 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
+          <t>最終電子接受者</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>化學滲透</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
           <t>質子梯度</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>解偶聯劑</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>(標圖:w15_etc_labeled) 標號5是什麼?</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>ATP合成酶</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>細胞色素c</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>複合體III</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>複合體I</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>(標圖:w15_chemiosmosis_labeled) 標號1代表的是什麼?</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>化學滲透</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>最終電子接受者</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>解偶聯劑</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>質子梯度</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>呼吸鏈</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>電子傳遞鏈</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>哪一個配對正確?</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>複合體I—直接生成ATP</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>複合體IV—將電子交給氧生成水</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>複合體III—是最終電子接受者</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>ATP合成酶—用電子傳遞產生FADH2</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>一分子葡萄糖完整氧化(醣解+TCA+氧化磷酸化)約可產生多少ATP?</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>30-32個ATP</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>2個ATP</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>36-38個ATP</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>8個ATP</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
     </row>
